--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_4.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754031464_h_4.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01759531771004896</v>
+        <v>0.01152477246900132</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008431490956486723</v>
+        <v>0.008423128287666226</v>
       </c>
       <c r="C2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>18121644</v>
+        <v>4455264</v>
       </c>
       <c r="L2" t="n">
-        <v>10597941</v>
+        <v>2535591</v>
       </c>
       <c r="M2" t="n">
-        <v>2650905</v>
+        <v>612371</v>
       </c>
       <c r="N2" t="n">
-        <v>132603</v>
+        <v>25951</v>
       </c>
       <c r="O2" t="n">
-        <v>1614012</v>
+        <v>380961</v>
       </c>
       <c r="P2" t="n">
-        <v>642665</v>
+        <v>149648</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999948143959045</v>
+        <v>0.9999960660934448</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9049053192138672</v>
+        <v>0.8835134506225586</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7958084344863892</v>
+        <v>0.7588281631469727</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7423143982887268</v>
+        <v>0.697833240032196</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5240210294723511</v>
+        <v>0.3911169469356537</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7900468707084656</v>
+        <v>0.7475481629371643</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8568489551544189</v>
+        <v>0.8361297845840454</v>
       </c>
       <c r="X2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>25185108</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>19203868</v>
+        <v>4809709</v>
       </c>
       <c r="AG2" t="n">
-        <v>11844967</v>
+        <v>2974674</v>
       </c>
       <c r="AH2" t="n">
-        <v>3194227</v>
+        <v>799643</v>
       </c>
       <c r="AI2" t="n">
-        <v>235673</v>
+        <v>59000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1835708</v>
+        <v>459265</v>
       </c>
       <c r="AK2" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9565847516059875</v>
+        <v>0.956451416015625</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.911228358745575</v>
+        <v>0.9113048315048218</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.85814368724823</v>
+        <v>0.8578755855560303</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6624941229820251</v>
+        <v>0.6619618535041809</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020473957061768</v>
+        <v>0.9019733667373657</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314249157905579</v>
+        <v>0.931433379650116</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.004238021279440194</v>
+        <v>0.002709935815991044</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002022527131276332</v>
+        <v>0.002019936826367219</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>18121644</v>
+        <v>4455264</v>
       </c>
       <c r="E3" t="n">
-        <v>1897492</v>
+        <v>560010</v>
       </c>
       <c r="F3" t="n">
-        <v>30558</v>
+        <v>6819</v>
       </c>
       <c r="G3" t="n">
-        <v>3541</v>
+        <v>772</v>
       </c>
       <c r="H3" t="n">
-        <v>1647</v>
+        <v>352</v>
       </c>
       <c r="I3" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>39960361</v>
+        <v>10016597</v>
       </c>
       <c r="K3" t="n">
-        <v>43186285</v>
+        <v>10718968</v>
       </c>
       <c r="L3" t="n">
-        <v>49410183</v>
+        <v>12254848</v>
       </c>
       <c r="M3" t="n">
-        <v>60501137</v>
+        <v>15131848</v>
       </c>
       <c r="N3" t="n">
-        <v>64669131</v>
+        <v>16200009</v>
       </c>
       <c r="O3" t="n">
-        <v>62680741</v>
+        <v>15691569</v>
       </c>
       <c r="P3" t="n">
-        <v>64265040</v>
+        <v>16106925</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9035996794700623</v>
+        <v>0.8869323134422302</v>
       </c>
       <c r="S3" t="n">
-        <v>0.814214289188385</v>
+        <v>0.7756741046905518</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7117989063262939</v>
+        <v>0.6566340327262878</v>
       </c>
       <c r="U3" t="n">
-        <v>0.372456282377243</v>
+        <v>0.2909598648548126</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7927604913711548</v>
+        <v>0.7478944659233093</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8311842083930969</v>
+        <v>0.7739906907081604</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>19203868</v>
+        <v>4809709</v>
       </c>
       <c r="Z3" t="n">
-        <v>789624</v>
+        <v>198076</v>
       </c>
       <c r="AA3" t="n">
-        <v>34065</v>
+        <v>8559</v>
       </c>
       <c r="AB3" t="n">
-        <v>27091</v>
+        <v>6810</v>
       </c>
       <c r="AC3" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>39960492</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>44219072</v>
+        <v>11087378</v>
       </c>
       <c r="AG3" t="n">
-        <v>50975509</v>
+        <v>12771195</v>
       </c>
       <c r="AH3" t="n">
-        <v>60893342</v>
+        <v>15264532</v>
       </c>
       <c r="AI3" t="n">
-        <v>64669514</v>
+        <v>16210280</v>
       </c>
       <c r="AJ3" t="n">
-        <v>62910323</v>
+        <v>15770309</v>
       </c>
       <c r="AK3" t="n">
-        <v>64319392</v>
+        <v>16123000</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575625658035278</v>
+        <v>0.9574934840202332</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100202918052673</v>
+        <v>0.909995973110199</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.85768723487854</v>
+        <v>0.857442319393158</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6619600653648376</v>
+        <v>0.6615017056465149</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016517400741577</v>
+        <v>0.9016192555427551</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313249588012695</v>
+        <v>0.9312165975570679</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04953244913381025</v>
+        <v>0.03613891287992572</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03190658617682631</v>
+        <v>0.0318805782860274</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>1802455</v>
+        <v>555605</v>
       </c>
       <c r="E4" t="n">
-        <v>10597941</v>
+        <v>2535591</v>
       </c>
       <c r="F4" t="n">
-        <v>559052</v>
+        <v>160565</v>
       </c>
       <c r="G4" t="n">
-        <v>14851</v>
+        <v>4837</v>
       </c>
       <c r="H4" t="n">
-        <v>39115</v>
+        <v>11598</v>
       </c>
       <c r="I4" t="n">
-        <v>2743</v>
+        <v>691</v>
       </c>
       <c r="J4" t="n">
-        <v>131</v>
+        <v>25</v>
       </c>
       <c r="K4" t="n">
-        <v>1904367</v>
+        <v>587403</v>
       </c>
       <c r="L4" t="n">
-        <v>2719260</v>
+        <v>805865</v>
       </c>
       <c r="M4" t="n">
-        <v>920230</v>
+        <v>265161</v>
       </c>
       <c r="N4" t="n">
-        <v>120446</v>
+        <v>40400</v>
       </c>
       <c r="O4" t="n">
-        <v>428920</v>
+        <v>128653</v>
       </c>
       <c r="P4" t="n">
-        <v>107368</v>
+        <v>29329</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999974370002747</v>
+        <v>0.9999980330467224</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9042519927024841</v>
+        <v>0.8852195143699646</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8049060702323914</v>
+        <v>0.7671586871147156</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7267365455627441</v>
+        <v>0.676607072353363</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4354263246059418</v>
+        <v>0.3336848020553589</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7914013266563416</v>
+        <v>0.7477213144302368</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8438215255737305</v>
+        <v>0.803861141204834</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>813684</v>
+        <v>204447</v>
       </c>
       <c r="Z4" t="n">
-        <v>11844967</v>
+        <v>2974674</v>
       </c>
       <c r="AA4" t="n">
-        <v>330759</v>
+        <v>83051</v>
       </c>
       <c r="AB4" t="n">
-        <v>21895</v>
+        <v>5499</v>
       </c>
       <c r="AC4" t="n">
-        <v>4580</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>272</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>871580</v>
+        <v>218993</v>
       </c>
       <c r="AG4" t="n">
-        <v>1153934</v>
+        <v>289518</v>
       </c>
       <c r="AH4" t="n">
-        <v>528025</v>
+        <v>132477</v>
       </c>
       <c r="AI4" t="n">
-        <v>120063</v>
+        <v>30129</v>
       </c>
       <c r="AJ4" t="n">
-        <v>199338</v>
+        <v>49913</v>
       </c>
       <c r="AK4" t="n">
-        <v>53016</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570733904838562</v>
+        <v>0.9569721221923828</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106239080429077</v>
+        <v>0.9106499552726746</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579154014587402</v>
+        <v>0.857658863067627</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6622269749641418</v>
+        <v>0.6617317199707031</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018495678901672</v>
+        <v>0.9017962217330933</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313749670982361</v>
+        <v>0.9313249588012695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>62033</v>
+        <v>19514</v>
       </c>
       <c r="E5" t="n">
-        <v>714388</v>
+        <v>214519</v>
       </c>
       <c r="F5" t="n">
-        <v>2650905</v>
+        <v>612371</v>
       </c>
       <c r="G5" t="n">
-        <v>52402</v>
+        <v>16220</v>
       </c>
       <c r="H5" t="n">
-        <v>229600</v>
+        <v>65584</v>
       </c>
       <c r="I5" t="n">
-        <v>14890</v>
+        <v>4381</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1933304</v>
+        <v>567965</v>
       </c>
       <c r="L5" t="n">
-        <v>2418216</v>
+        <v>733296</v>
       </c>
       <c r="M5" t="n">
-        <v>1073328</v>
+        <v>320220</v>
       </c>
       <c r="N5" t="n">
-        <v>223420</v>
+        <v>63240</v>
       </c>
       <c r="O5" t="n">
-        <v>421927</v>
+        <v>128417</v>
       </c>
       <c r="P5" t="n">
-        <v>130527</v>
+        <v>43698</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999979734420776</v>
+        <v>0.9999984502792358</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9410908818244934</v>
+        <v>0.9292470216751099</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9211385846138</v>
+        <v>0.9057441353797913</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9693984389305115</v>
+        <v>0.9641521573066711</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9947215914726257</v>
+        <v>0.9936532378196716</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9869393110275269</v>
+        <v>0.9842574000358582</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9963482618331909</v>
+        <v>0.9955279231071472</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>31947</v>
+        <v>8028</v>
       </c>
       <c r="Z5" t="n">
-        <v>339404</v>
+        <v>85185</v>
       </c>
       <c r="AA5" t="n">
-        <v>3194227</v>
+        <v>799643</v>
       </c>
       <c r="AB5" t="n">
-        <v>39720</v>
+        <v>9960</v>
       </c>
       <c r="AC5" t="n">
-        <v>116403</v>
+        <v>29142</v>
       </c>
       <c r="AD5" t="n">
-        <v>2532</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>851080</v>
+        <v>213520</v>
       </c>
       <c r="AG5" t="n">
-        <v>1171190</v>
+        <v>294213</v>
       </c>
       <c r="AH5" t="n">
-        <v>530006</v>
+        <v>132948</v>
       </c>
       <c r="AI5" t="n">
-        <v>120350</v>
+        <v>30191</v>
       </c>
       <c r="AJ5" t="n">
-        <v>200231</v>
+        <v>50113</v>
       </c>
       <c r="AK5" t="n">
-        <v>53099</v>
+        <v>13299</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735567569732666</v>
+        <v>0.9735135436058044</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643087983131409</v>
+        <v>0.9642531871795654</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837589859962463</v>
+        <v>0.9837457537651062</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9963061213493347</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.993866503238678</v>
+        <v>0.9938745498657227</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983711242675781</v>
+        <v>0.9983739256858826</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>39403</v>
+        <v>12232</v>
       </c>
       <c r="E6" t="n">
-        <v>64999</v>
+        <v>18286</v>
       </c>
       <c r="F6" t="n">
-        <v>74536</v>
+        <v>20437</v>
       </c>
       <c r="G6" t="n">
-        <v>132603</v>
+        <v>25951</v>
       </c>
       <c r="H6" t="n">
-        <v>41086</v>
+        <v>11413</v>
       </c>
       <c r="I6" t="n">
-        <v>3360</v>
+        <v>861</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>25726</v>
+        <v>6462</v>
       </c>
       <c r="Z6" t="n">
-        <v>21345</v>
+        <v>5366</v>
       </c>
       <c r="AA6" t="n">
-        <v>43462</v>
+        <v>10898</v>
       </c>
       <c r="AB6" t="n">
-        <v>235673</v>
+        <v>59000</v>
       </c>
       <c r="AC6" t="n">
-        <v>27893</v>
+        <v>6984</v>
       </c>
       <c r="AD6" t="n">
-        <v>1924</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>388</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>40364</v>
+        <v>12489</v>
       </c>
       <c r="F7" t="n">
-        <v>247746</v>
+        <v>74781</v>
       </c>
       <c r="G7" t="n">
-        <v>47069</v>
+        <v>17730</v>
       </c>
       <c r="H7" t="n">
-        <v>1614012</v>
+        <v>380961</v>
       </c>
       <c r="I7" t="n">
-        <v>86321</v>
+        <v>23387</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>111</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>3237</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>118419</v>
+        <v>29639</v>
       </c>
       <c r="AB7" t="n">
-        <v>30296</v>
+        <v>7594</v>
       </c>
       <c r="AC7" t="n">
-        <v>1835708</v>
+        <v>459265</v>
       </c>
       <c r="AD7" t="n">
-        <v>48168</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>88</v>
+        <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>2017</v>
+        <v>561</v>
       </c>
       <c r="F8" t="n">
-        <v>8338</v>
+        <v>2559</v>
       </c>
       <c r="G8" t="n">
-        <v>2583</v>
+        <v>841</v>
       </c>
       <c r="H8" t="n">
-        <v>117472</v>
+        <v>39706</v>
       </c>
       <c r="I8" t="n">
-        <v>642665</v>
+        <v>149648</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1320</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>1061</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>50282</v>
+        <v>12594</v>
       </c>
       <c r="AD8" t="n">
-        <v>720093</v>
+        <v>180047</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
